--- a/src/test/resources/writer/style.xlsx
+++ b/src/test/resources/writer/style.xlsx
@@ -106,7 +106,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="28">
+  <fonts count="30">
     <font>
       <sz val="11.0"/>
       <color indexed="8"/>
@@ -203,6 +203,10 @@
     <font>
       <name val="Calibri"/>
       <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
       <color rgb="FFFFC000"/>
     </font>
     <font>
@@ -217,6 +221,10 @@
       <name val="Calibri"/>
       <sz val="11.0"/>
       <i val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -286,7 +294,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyBorder="true" applyFont="true"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyBorder="true" applyFont="true"/>
@@ -319,24 +327,26 @@
       <alignment horizontal="fill"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyAlignment="true" applyFont="true">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyAlignment="true" applyFont="true">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true">
       <alignment wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true"/>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyAlignment="true" applyFont="true">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyAlignment="true" applyFont="true">
       <alignment vertical="justify"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyAlignment="true" applyFont="true">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyAlignment="true" applyFont="true">
       <alignment horizontal="justify"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="4" xfId="0" applyBorder="true" applyFont="true"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="4" xfId="0" applyBorder="true" applyFont="true"/>
   </cellXfs>
 </styleSheet>
 </file>
@@ -346,7 +356,6 @@
   <dimension ref="A1:W2"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="12" max="12" width="50.0" customWidth="true"/>
     <col min="1" max="1" width="6.0390625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="9.51171875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="12.55078125" customWidth="true" bestFit="true"/>
@@ -358,6 +367,7 @@
     <col min="9" max="9" width="21.54296875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="17.30859375" customWidth="true" bestFit="true"/>
     <col min="11" max="11" width="63.3671875" customWidth="true" bestFit="true"/>
+    <col min="12" max="12" width="38.35546875" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="43.1015625" customWidth="true" bestFit="true"/>
     <col min="15" max="15" width="35.8125" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="41.21484375" customWidth="true" bestFit="true"/>
@@ -371,105 +381,105 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="s" s="1">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s" s="2">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s" s="3">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s" s="4">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s" s="5">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s" s="8">
+      <c r="F1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s" s="14">
+      <c r="G1" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s" s="25">
+      <c r="H1" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s" s="26">
+      <c r="I1" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s" s="17">
+      <c r="J1" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s" s="19">
+      <c r="K1" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s" s="20">
+      <c r="L1" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s" s="20">
+      <c r="M1" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s" s="20">
+      <c r="N1" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s" s="27">
+      <c r="O1" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s" s="1">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s" s="20">
+      <c r="Q1" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s" s="20">
+      <c r="R1" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s" s="20">
+      <c r="S1" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="T1" t="s" s="21">
+      <c r="T1" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="U1" t="s" s="11">
+      <c r="U1" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="V1" t="s" s="22">
+      <c r="V1" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="W1" t="s" s="12">
+      <c r="W1" s="12" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="s" s="13">
+      <c r="A2" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="B2" t="s" s="6">
+      <c r="B2" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C2" t="s" s="9">
+      <c r="C2" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D2" t="s" s="23">
+      <c r="D2" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="E2" t="s" s="18">
+      <c r="E2" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="F2" t="s" s="7">
+      <c r="F2" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G2" t="s" s="15">
+      <c r="G2" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="H2" t="s" s="24">
+      <c r="H2" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="I2" t="s" s="16">
+      <c r="I2" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="J2" t="s" s="10">
+      <c r="J2" s="10" t="s">
         <v>28</v>
       </c>
     </row>
